--- a/templates/class_schedule_template.xlsx
+++ b/templates/class_schedule_template.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># Legend: one row per weekly class block. Day = Monday–Sunday (or Mon/Tue...). Times in 24-hour HH:MM. Class Name optional. Delete this row and the example row before or after adding real data — rows starting with # are ignored by the tool.</t>
+          <t># Legend: one row per weekly class block. Day = Monday–Sunday (or Mon/Tue...). Times in 24-hour HH:MM, in the campus local time you selected in the app. Class Name optional. Delete this row and the example row before or after adding real data — rows starting with # are ignored by the tool.</t>
         </is>
       </c>
     </row>

--- a/templates/class_schedule_template.xlsx
+++ b/templates/class_schedule_template.xlsx
@@ -436,32 +436,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Class Block</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>End Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Class Name</t>
         </is>
@@ -470,27 +476,275 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># Legend: one row per weekly class block. Day = Monday–Sunday (or Mon/Tue...). Times in 24-hour HH:MM, in the campus local time you selected in the app. Class Name optional. Delete this row and the example row before or after adding real data — rows starting with # are ignored by the tool.</t>
+          <t># Legend: one row per class. Class Block is the cohort this class belongs to — spell it identically on every row of that block, and on the matching students in the student list. Each class block must total exactly 15 hours of class across the whole block (not per week). Day = Monday–Sunday (or Mon/Tue...). Times in 24-hour HH:MM, in the campus local time you selected in the app. Class Name optional. Rows starting with # are ignored.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Block A</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Fundamentals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Block B</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Marketing Fundamentals</t>
         </is>
